--- a/reports/tablas_evaluacion_final.xlsx
+++ b/reports/tablas_evaluacion_final.xlsx
@@ -506,10 +506,10 @@
         <v>0.835820895522388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9849466577253239</v>
+        <v>0.9849466577253236</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8754704661190621</v>
+        <v>0.8754704661190619</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6626016260162602</v>
+        <v>0.6582792207792207</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7970660146699267</v>
+        <v>0.793930494371023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9671547943886902</v>
+        <v>0.9669035681438755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6648596887573082</v>
+        <v>0.6605959361161341</v>
       </c>
     </row>
     <row r="3">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9979633401221996</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999975051027047</v>
+        <v>0.999998962781352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9986897802862327</v>
+        <v>0.9994613550052277</v>
       </c>
     </row>
     <row r="4">
@@ -710,19 +710,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.9967558799675588</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9979633401221996</v>
+        <v>0.9971602434077079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9996084077441783</v>
+        <v>0.999997482743577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.99598869390091</v>
+        <v>0.999102283332354</v>
       </c>
     </row>
     <row r="5">
@@ -737,19 +737,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.003030129781030244</v>
+        <v>0.002461517898910695</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2154471544715447</v>
+        <v>0.1793831168831169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005976207926932401</v>
+        <v>0.004856395719339881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5587583284256358</v>
+        <v>0.5691047622444836</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004321102157328815</v>
+        <v>0.005096685132794548</v>
       </c>
     </row>
     <row r="6">
@@ -764,19 +764,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01385511508228242</v>
+        <v>0.01353628583701387</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02733002398349043</v>
+        <v>0.02671013311600109</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9982700765984647</v>
+        <v>0.9989947000954323</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9959472485891354</v>
+        <v>0.9975726795811553</v>
       </c>
     </row>
   </sheetData>
@@ -878,10 +878,10 @@
         <v>0.835820895522388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9849466577253239</v>
+        <v>0.9849466577253236</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8754704661190621</v>
+        <v>0.8754704661190619</v>
       </c>
     </row>
     <row r="4">
@@ -980,16 +980,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6626016260162602</v>
+        <v>0.6582792207792207</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7970660146699267</v>
+        <v>0.793930494371023</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9671547943886902</v>
+        <v>0.9669035681438755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6648596887573082</v>
+        <v>0.6605959361161341</v>
       </c>
     </row>
     <row r="8">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9979633401221996</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999975051027047</v>
+        <v>0.999998962781352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9986897802862327</v>
+        <v>0.9994613550052277</v>
       </c>
     </row>
     <row r="9">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9967558799675588</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9979633401221996</v>
+        <v>0.9971602434077079</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9996084077441783</v>
+        <v>0.999997482743577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.99598869390091</v>
+        <v>0.999102283332354</v>
       </c>
     </row>
     <row r="10">
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003030129781030244</v>
+        <v>0.002461517898910695</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2154471544715447</v>
+        <v>0.1793831168831169</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005976207926932401</v>
+        <v>0.004856395719339881</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5587583284256358</v>
+        <v>0.5691047622444836</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004321102157328815</v>
+        <v>0.005096685132794548</v>
       </c>
     </row>
     <row r="11">
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01385511508228242</v>
+        <v>0.01353628583701387</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02733002398349043</v>
+        <v>0.02671013311600109</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9982700765984647</v>
+        <v>0.9989947000954323</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9959472485891354</v>
+        <v>0.9975726795811553</v>
       </c>
     </row>
   </sheetData>
@@ -1151,19 +1151,19 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002953181272509004</v>
+        <v>0.002975205813243047</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005888971345127236</v>
+        <v>0.005932760443127123</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9671547943886902</v>
+        <v>0.9669035681438755</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6648596887573082</v>
+        <v>0.6605959361161341</v>
       </c>
     </row>
     <row r="3">
@@ -1171,19 +1171,19 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.006738173817381738</v>
+        <v>0.006843881290783946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.9943181818181818</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0133857837512976</v>
+        <v>0.01359419389204545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9671547943886902</v>
+        <v>0.9669035681438755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6648596887573082</v>
+        <v>0.6605959361161341</v>
       </c>
     </row>
     <row r="4">
@@ -1194,16 +1194,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6626016260162602</v>
+        <v>0.6582792207792207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7970660146699267</v>
+        <v>0.793930494371023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9671547943886902</v>
+        <v>0.9669035681438755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6648596887573082</v>
+        <v>0.6605959361161341</v>
       </c>
     </row>
   </sheetData>
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.003030129781030244</v>
+        <v>0.002461517898910695</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2154471544715447</v>
+        <v>0.1793831168831169</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005976207926932401</v>
+        <v>0.004856395719339881</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5587583284256358</v>
+        <v>0.5691047622444836</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004321102157328815</v>
+        <v>0.005096685132794548</v>
       </c>
     </row>
     <row r="5">
@@ -1350,19 +1350,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.152</v>
+        <v>0.1203776553894571</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.1241883116883117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1532258064516129</v>
+        <v>0.1222532960447463</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9278015319010575</v>
+        <v>0.9252581127972588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06204032524408991</v>
+        <v>0.05471136601025749</v>
       </c>
     </row>
   </sheetData>
@@ -1509,19 +1509,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5361050328227571</v>
+        <v>0.5229787234042553</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6970128022759602</v>
+        <v>0.6862088218872139</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9984818016860303</v>
+        <v>0.999108214223958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9959489565221646</v>
+        <v>0.997575811119357</v>
       </c>
     </row>
     <row r="6">
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.1241883116883117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9996084077441783</v>
+        <v>0.9999963331169969</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9959886939009102</v>
+        <v>0.9971084585129898</v>
       </c>
     </row>
     <row r="7">
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9959349593495935</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9979633401221996</v>
+        <v>0.997564935064935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9984817163903962</v>
+        <v>0.9991596553297568</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9959489557385252</v>
+        <v>0.9958902653961892</v>
       </c>
     </row>
   </sheetData>
